--- a/ledwave-comercial/LedWave_Playbook_Resumido.xlsx
+++ b/ledwave-comercial/LedWave_Playbook_Resumido.xlsx
@@ -1336,13 +1336,13 @@
     <t xml:space="preserve">Ano de fundação + vida útil dos painéis</t>
   </si>
   <si>
-    <t xml:space="preserve">No hall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Descrever com o comercial]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Definir]</t>
+    <t xml:space="preserve">Know-how</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mais de 15 anos fabricando, instalando e operando painéis de LED: sabemos o que funciona em cada tipo de espaço, do PDV ao maior painel da América Latina.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histórico de projetos + Boulevard.Live</t>
   </si>
   <si>
     <t xml:space="preserve">Prova social</t>
@@ -1888,10 +1888,10 @@
     <t xml:space="preserve">Beto Carrero World</t>
   </si>
   <si>
-    <t xml:space="preserve">Cesstto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Confirmar nome e segmento]</t>
+    <t xml:space="preserve">Cestto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Confirmar segmento]</t>
   </si>
   <si>
     <t xml:space="preserve">Experiência; Retrofit / arquitetura</t>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>397</v>
       </c>
@@ -8621,7 +8621,7 @@
         <v>399</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>393</v>
+        <v>22</v>
       </c>
       <c r="E11" s="8"/>
     </row>

--- a/ledwave-comercial/LedWave_Playbook_Resumido.xlsx
+++ b/ledwave-comercial/LedWave_Playbook_Resumido.xlsx
@@ -2544,7 +2544,7 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <color rgb="FF1B1340"/>
+      <color rgb="FF3D3D3D"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2580,7 +2580,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF1B1340"/>
+      <color rgb="FF3D3D3D"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2595,7 +2595,7 @@
     <font>
       <i val="true"/>
       <sz val="10"/>
-      <color rgb="FFC2185B"/>
+      <color rgb="FF8A5CF6"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2603,7 +2603,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFC2185B"/>
+      <color rgb="FF8A5CF6"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2618,8 +2618,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B1340"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor rgb="FF3D3D3D"/>
+        <bgColor rgb="FF333300"/>
       </patternFill>
     </fill>
     <fill>
@@ -2630,8 +2630,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC2185B"/>
-        <bgColor rgb="FFB00020"/>
+        <fgColor rgb="FF8A5CF6"/>
+        <bgColor rgb="FF9999FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -2832,7 +2832,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC2185B"/>
+          <fgColor rgb="FF8A5CF6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2913,7 +2913,7 @@
       <rgbColor rgb="FFD0CCE0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FFC2185B"/>
+      <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF8D6"/>
       <rgbColor rgb="FFF5F5F7"/>
       <rgbColor rgb="FF660066"/>
@@ -2942,7 +2942,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF8A5CF6"/>
       <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -2951,7 +2951,7 @@
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1B1340"/>
+      <rgbColor rgb="FF3D3D3D"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -3147,7 +3147,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FFC2185B"/>
+    <tabColor rgb="FF8A5CF6"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
@@ -3364,7 +3364,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FFC2185B"/>
+    <tabColor rgb="FF8A5CF6"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K304"/>
@@ -6951,7 +6951,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FFC2185B"/>
+    <tabColor rgb="FF8A5CF6"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F15"/>
@@ -7250,7 +7250,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FFC2185B"/>
+    <tabColor rgb="FF8A5CF6"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M21"/>
@@ -8089,7 +8089,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FFC2185B"/>
+    <tabColor rgb="FF8A5CF6"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I13"/>
@@ -8457,7 +8457,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1B1340"/>
+    <tabColor rgb="FF3D3D3D"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
@@ -8812,7 +8812,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1B1340"/>
+    <tabColor rgb="FF3D3D3D"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F43"/>
@@ -9492,7 +9492,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1B1340"/>
+    <tabColor rgb="FF3D3D3D"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H19"/>
@@ -9782,7 +9782,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1B1340"/>
+    <tabColor rgb="FF3D3D3D"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
@@ -10267,7 +10267,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1B1340"/>
+    <tabColor rgb="FF3D3D3D"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
